--- a/main/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:43:11+00:00</t>
+    <t>2026-09-14T07:43:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:43:38+00:00</t>
+    <t>2026-10-01T07:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T07:35:36+00:00</t>
+    <t>2026-10-14T13:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -722,56 +722,56 @@
     <t>SubstanceAdministration.consumable</t>
   </si>
   <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/InfrastructureRoot
+</t>
+  </si>
+  <si>
+    <t>Antigène</t>
+  </si>
+  <si>
+    <t>The consumable participation is used to bring in the LabeledDrug or Material entity that describes the administered substance. The LabeledDrug class, which is an Entity class playing the Role of Manufactured Product, identifies the drug that is consumed in the substance administration. The medication is identified by means of the LabeledDrug.code or the LabeledDrug.name. The Material entity is used to identify non-drug administered substances such as vaccines and blood products.</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.nullFlavor</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.realmCode</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId.nullFlavor</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId.displayable</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId.root</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeId.extension</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.templateId</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.typeCode</t>
+  </si>
+  <si>
+    <t>CSM</t>
+  </si>
+  <si>
+    <t>http://hl7.org/cda/stds/core/ValueSet/CDAParticipationType|2.0.3-sd</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.manufacturedProduct</t>
+  </si>
+  <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ManufacturedProduct {https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-produit-de-sante|0.1.0}
-</t>
-  </si>
-  <si>
-    <t>Antigène</t>
-  </si>
-  <si>
-    <t>The consumable participation is used to bring in the LabeledDrug or Material entity that describes the administered substance. The LabeledDrug class, which is an Entity class playing the Role of Manufactured Product, identifies the drug that is consumed in the substance administration. The medication is identified by means of the LabeledDrug.code or the LabeledDrug.name. The Material entity is used to identify non-drug administered substances such as vaccines and blood products.</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.nullFlavor</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.realmCode</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId.nullFlavor</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId.displayable</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId.root</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeId.extension</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.templateId</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.typeCode</t>
-  </si>
-  <si>
-    <t>CSM</t>
-  </si>
-  <si>
-    <t>http://hl7.org/cda/stds/core/ValueSet/CDAParticipationType|2.0.3-sd</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration.consumable.manufacturedProduct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ManufacturedProduct
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T13:15:36+00:00</t>
+    <t>2026-10-15T09:41:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:41:25+00:00</t>
+    <t>2026-10-15T10:11:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:11:14+00:00</t>
+    <t>2026-10-15T11:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:51:04+00:00</t>
+    <t>2026-10-15T13:36:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:36:09+00:00</t>
+    <t>2026-10-15T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T15:46:20+00:00</t>
+    <t>2026-10-16T07:40:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T07:40:35+00:00</t>
+    <t>2026-10-16T08:34:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T08:34:24+00:00</t>
+    <t>2026-10-16T09:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dose-antigene.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:04:08+00:00</t>
+    <t>2026-10-16T11:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
